--- a/artfynd/A 18075-2026 artfynd.xlsx
+++ b/artfynd/A 18075-2026 artfynd.xlsx
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>384833</v>
+        <v>236000</v>
       </c>
       <c r="B2" t="n">
-        <v>89831</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>634130.3434093941</v>
+        <v>634065</v>
       </c>
       <c r="R2" t="n">
-        <v>7010109.097615974</v>
+        <v>7010120</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2008-09-11</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2008-09-29</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,7 +762,7 @@
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>1 substratenheter # grov granlåga</t>
+          <t>1 substratenheter # granlåga</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -799,15 +784,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>236000</v>
+        <v>384833</v>
       </c>
       <c r="B3" t="n">
-        <v>89672</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -815,21 +795,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -839,10 +819,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>634065.1706858135</v>
+        <v>634130</v>
       </c>
       <c r="R3" t="n">
-        <v>7010120.396581818</v>
+        <v>7010109</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,19 +852,9 @@
           <t>2008-09-11</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2008-09-29</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -901,7 +871,7 @@
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>1 substratenheter # granlåga</t>
+          <t>1 substratenheter # grov granlåga</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>

--- a/artfynd/A 18075-2026 artfynd.xlsx
+++ b/artfynd/A 18075-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -781,6 +786,11 @@
           <t>Skogsbruksplan Björkå bruk</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/236000</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -890,8 +900,17 @@
           <t>Skogsbruksplan Björkå bruk</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/384833</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>